--- a/assets/constructions/examples/ctd_me2.xlsx
+++ b/assets/constructions/examples/ctd_me2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,11 +659,46 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>fhamin</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>fhamax</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SGNF1104016</t>
+          <t>SEME7308042E</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -673,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SGNF1</t>
+          <t>SEME73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -681,38 +716,36 @@
           <t>H</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -738,13 +771,13 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Nano Grain Carbide</t>
+          <t>Micro Grain Carbide</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Y-Coating</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -752,20 +785,22 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>8</v>
+      </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
@@ -777,7 +812,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2020: www.yg1.co.kr/toolselection/main/</t>
+          <t>2017 - YG1 - YE-4G13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -786,61 +821,90 @@
         </is>
       </c>
       <c r="AS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
         <v>1</v>
       </c>
-      <c r="AT2" t="b">
-        <v>0</v>
+      <c r="AV2" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>8714.4</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEM84501505</t>
+          <t>6803 9.700</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>GUHRING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEM84</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MKH</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>PMKNS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9.5</v>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J3" t="n">
-        <v>2.3</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3</v>
+        <v>14</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.3</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>24.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -861,39 +925,45 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0/-0,03</t>
+          <t>h10</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Micro Grain Carbide</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Y-Coating</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>Signum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>DIN 6527 K</t>
+        </is>
+      </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
@@ -905,7 +975,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2017 - YG1 - YE-4G13</t>
+          <t>2019 - Guhring Фрезерный инструмент New Level</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -914,26 +984,39 @@
         </is>
       </c>
       <c r="AS3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H602411-8</t>
+          <t>SGED3000502</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>H602411</t>
+          <t>SGED30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -943,32 +1026,32 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>0.7</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>0.7</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -989,47 +1072,45 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>h10</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
+          <t>0/-0,012</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Nano Grain Carbide</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>DIN 6527 L</t>
-        </is>
-      </c>
+          <t>DLC</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AB4" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>7.6</v>
+        <v>0.45</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>2</v>
-      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
@@ -1037,7 +1118,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2017/Общий каталог WALTER 2017</t>
+          <t>2017 - YG1 - General catalogue</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1049,23 +1130,44 @@
         <v>0</v>
       </c>
       <c r="AT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
         <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>6713</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H602411-1</t>
+          <t>SGED3001012</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>H602411</t>
+          <t>SGED30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1081,26 +1183,26 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N5" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1121,47 +1223,45 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>h10</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
+          <t>0/-0,012</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Nano Grain Carbide</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>DIN 6527 L</t>
-        </is>
-      </c>
+          <t>DLC</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
@@ -1169,7 +1269,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2017/Общий каталог WALTER 2017</t>
+          <t>2017 - YG1 - General catalogue</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1181,56 +1281,79 @@
         <v>0</v>
       </c>
       <c r="AT5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
         <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>6098.88</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>END MILL Ø15 FA405WE V-MAXX</t>
+          <t>C2SAD1000N300</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>MITSUBISHI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FA405WE</t>
+          <t>C2SA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>12</v>
+      </c>
       <c r="N6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>HB-12</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1240,54 +1363,44 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>HSSY</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0/-0,03</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>V-MAXX</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>DIN 844 K</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>37</v>
-      </c>
+        <v>9.4</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
@@ -1299,12 +1412,12 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2022/Vergnano-End-Mills-Catalogue-65.pdf</t>
+          <t>2020 / Mitsubishi Website</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AS6" t="b">
@@ -1312,6 +1425,19 @@
       </c>
       <c r="AT6" t="b">
         <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
   </sheetData>
